--- a/Linkedin_Process/Data/Templates/JobOffers.xlsx
+++ b/Linkedin_Process/Data/Templates/JobOffers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\UiPath\RPA_Projects\Linkedin_Process\Data\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AE2C35-67C1-4D96-98A3-FCE95C2E5BCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E9DD97-83A6-42EB-993C-08C355F4828F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7644" yWindow="1908" windowWidth="23220" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="31176" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Offers" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Name Offer</t>
   </si>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t>SkillsMissing</t>
+  </si>
+  <si>
+    <t>CanWorkFromColombia</t>
+  </si>
+  <si>
+    <t>KeywordsFromOffer</t>
+  </si>
+  <si>
+    <t>WouldIfitWithThisOffer</t>
+  </si>
+  <si>
+    <t>Additional URL</t>
   </si>
 </sst>
 </file>
@@ -405,25 +417,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.21875" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" customWidth="1"/>
-    <col min="12" max="12" width="20.77734375" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="45.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" customWidth="1"/>
+    <col min="6" max="6" width="31.1796875" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="11" width="18.6328125" customWidth="1"/>
+    <col min="12" max="12" width="20.81640625" customWidth="1"/>
+    <col min="13" max="14" width="14.6328125" customWidth="1"/>
+    <col min="15" max="15" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,6 +477,18 @@
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
